--- a/public/templates/test_input/Input_bao_cao_21.xlsx
+++ b/public/templates/test_input/Input_bao_cao_21.xlsx
@@ -759,136 +759,84 @@
     <row r="4">
       <c r="A4" s="27" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>11/07/2026</t>
         </is>
       </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>Ca 3</t>
-        </is>
+      <c r="B4" s="1" t="n">
+        <v>2</v>
       </c>
       <c r="C4" s="15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D4" s="11" t="inlineStr">
         <is>
-          <t>PX Đào lò</t>
+          <t>PX Khai thác 3</t>
         </is>
       </c>
       <c r="E4" s="1" t="inlineStr">
         <is>
-          <t>Lê Văn C</t>
+          <t>Trần Văn B</t>
         </is>
       </c>
       <c r="F4" s="2" t="n">
         <v>14</v>
       </c>
       <c r="G4" s="28" t="n">
-        <v>647</v>
+        <v>248</v>
       </c>
       <c r="H4" s="28" t="n">
-        <v>13.3</v>
+        <v>12.3</v>
       </c>
       <c r="I4" s="28" t="n">
-        <v>2.5</v>
+        <v>1.1</v>
       </c>
       <c r="J4" s="28" t="n">
-        <v>11.4</v>
+        <v>8.5</v>
       </c>
       <c r="K4" s="28" t="n">
-        <v>5.9</v>
+        <v>6.5</v>
       </c>
       <c r="L4" s="28" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="M4" s="28" t="n">
-        <v>6.4</v>
+        <v>1.2</v>
       </c>
       <c r="N4" s="28" t="n">
-        <v>3.4</v>
+        <v>5.2</v>
       </c>
       <c r="O4" s="28" t="n">
-        <v>0.4</v>
+        <v>4.8</v>
       </c>
       <c r="P4" s="28" t="n">
-        <v>2.2</v>
+        <v>3.7</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="R4" s="3" t="inlineStr"/>
-      <c r="S4" s="12" t="inlineStr">
-        <is>
-          <t>Ca làm việc bình thường.</t>
-        </is>
-      </c>
+      <c r="S4" s="12" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="27" t="inlineStr">
-        <is>
-          <t>03/07/2026</t>
-        </is>
-      </c>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>Ca 2</t>
-        </is>
-      </c>
-      <c r="C5" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" s="11" t="inlineStr">
-        <is>
-          <t>PX Đào lò</t>
-        </is>
-      </c>
-      <c r="E5" s="1" t="inlineStr">
-        <is>
-          <t>Lê Văn C</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="G5" s="28" t="n">
-        <v>205</v>
-      </c>
-      <c r="H5" s="28" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="I5" s="28" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="J5" s="28" t="n">
-        <v>15.4</v>
-      </c>
-      <c r="K5" s="28" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="L5" s="28" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="M5" s="28" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="N5" s="28" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="O5" s="28" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="P5" s="28" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="Q5" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="R5" s="3" t="inlineStr"/>
-      <c r="S5" s="12" t="inlineStr">
-        <is>
-          <t>Máy khoan gặp sự cố, tiến độ chậm.</t>
-        </is>
-      </c>
+      <c r="A5" s="27" t="n"/>
+      <c r="B5" s="1" t="n"/>
+      <c r="C5" s="15" t="n"/>
+      <c r="D5" s="11" t="n"/>
+      <c r="E5" s="1" t="n"/>
+      <c r="F5" s="2" t="n"/>
+      <c r="G5" s="28" t="n"/>
+      <c r="H5" s="28" t="n"/>
+      <c r="I5" s="28" t="n"/>
+      <c r="J5" s="28" t="n"/>
+      <c r="K5" s="28" t="n"/>
+      <c r="L5" s="28" t="n"/>
+      <c r="M5" s="28" t="n"/>
+      <c r="N5" s="28" t="n"/>
+      <c r="O5" s="28" t="n"/>
+      <c r="P5" s="28" t="n"/>
+      <c r="Q5" s="3" t="n"/>
+      <c r="R5" s="3" t="n"/>
+      <c r="S5" s="12" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="27" t="n"/>
